--- a/mau-excel/mau-hang-hoa_VuGia.xlsx
+++ b/mau-excel/mau-hang-hoa_VuGia.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:R4"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -415,7 +415,9 @@
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
     <col min="14" max="14" width="13.83203125" customWidth="1"/>
     <col min="15" max="15" width="17.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="24.83203125" customWidth="1"/>
+    <col min="17" max="17" width="23.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,12 @@
         <v>Đơn vị đóng gói</v>
       </c>
       <c r="P1" t="str">
+        <v>Trọng lượng/thùng (kg)</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Trọng lượng/viên (kg)</v>
+      </c>
+      <c r="R1" t="str">
         <v>Ghi chú</v>
       </c>
     </row>
@@ -512,9 +520,15 @@
         <v>140</v>
       </c>
       <c r="O2" t="str">
-        <v>hộp</v>
-      </c>
-      <c r="P2" t="str">
+        <v>thùng</v>
+      </c>
+      <c r="P2">
+        <v>28</v>
+      </c>
+      <c r="Q2">
+        <v>0.2</v>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
@@ -564,7 +578,13 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3" t="str">
+      <c r="P3">
+        <v>4.5</v>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
         <v>Ví dụ SKU để trống</v>
       </c>
     </row>
@@ -617,17 +637,23 @@
       <c r="P4" t="str">
         <v/>
       </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -666,12 +692,17 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>• "Trọng lượng/thùng (kg)" và/hoặc "Trọng lượng/viên (kg)": dùng để tính tổng trọng lượng đơn hàng (báo xe, ship). Chỉ cần điền 1 trong 2 cột; có cả 2 thì ưu tiên kg/viên. Ghi kiểu "28kg/ thùng", "140 viên/ thùng", "0,20" cũng được.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>• 3 cột giá: Giá lẻ / Giá sỉ / Giá CTV — tương ứng mức giá gán cho từng khách hàng.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A9"/>
   </ignoredErrors>
 </worksheet>
 </file>